--- a/Excel/ExclusiveDevourConfig.xlsx
+++ b/Excel/ExclusiveDevourConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="14">
   <si>
     <t>Id</t>
   </si>
@@ -53,13 +53,13 @@
     <t>150,30</t>
   </si>
   <si>
+    <t>450,90</t>
+  </si>
+  <si>
+    <t>1350,270</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>450,90</t>
-  </si>
-  <si>
-    <t>1350,270</t>
   </si>
   <si>
     <t>4050,810</t>
@@ -1129,10 +1129,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:6">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
+    <row r="7" customHeight="1" spans="3:6">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1143,13 +1140,10 @@
         <v>6</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1" spans="1:6">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
+    <row r="8" ht="20" customHeight="1" spans="3:6">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1160,12 +1154,15 @@
         <v>6</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="C9" s="1">
         <v>4</v>
@@ -1182,7 +1179,10 @@
     </row>
     <row r="10" customHeight="1" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="C10" s="1">
         <v>5</v>
@@ -1199,7 +1199,10 @@
     </row>
     <row r="11" customHeight="1" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="C11" s="1">
         <v>6</v>
@@ -1216,7 +1219,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 F3 E4 F4 E5 F5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:F3 E4:F5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,E3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/ExclusiveDevourConfig.xlsx
+++ b/Excel/ExclusiveDevourConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -27,11 +27,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="19">
   <si>
     <t>Id</t>
   </si>
   <si>
+    <t>Cycle</t>
+  </si>
+  <si>
     <t>Level</t>
   </si>
   <si>
@@ -59,16 +62,28 @@
     <t>1350,270</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>4050,810</t>
-  </si>
-  <si>
-    <t>12150,1230</t>
-  </si>
-  <si>
-    <t>36450,3690</t>
+    <t>4035,4010</t>
+  </si>
+  <si>
+    <t>150,300</t>
+  </si>
+  <si>
+    <t>450,900</t>
+  </si>
+  <si>
+    <t>1350,2700</t>
+  </si>
+  <si>
+    <t>4036,4010</t>
+  </si>
+  <si>
+    <t>150,1000</t>
+  </si>
+  <si>
+    <t>450,3000</t>
+  </si>
+  <si>
+    <t>1350,9000</t>
   </si>
 </sst>
 </file>
@@ -1064,163 +1079,223 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:F11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="5"/>
+  <dimension ref="C3:G17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="17.375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5" style="1" customWidth="1"/>
-    <col min="7" max="16379" width="9" style="1"/>
+    <col min="1" max="5" width="9" style="1"/>
+    <col min="6" max="6" width="17.3727272727273" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5" style="1" customWidth="1"/>
+    <col min="8" max="16380" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:7">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="G3" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:7">
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="G4" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:7">
       <c r="C5" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="E5" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="F5" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="3:6">
+    <row r="6" customHeight="1" spans="3:7">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>6</v>
+      <c r="E6" s="1">
+        <v>1</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="G6" s="4" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="7" customHeight="1" spans="3:6">
+    <row r="7" customHeight="1" spans="3:7">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
         <v>2</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>6</v>
-      </c>
       <c r="F7" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1" spans="3:6">
+    <row r="8" ht="20" customHeight="1" spans="3:7">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
         <v>3</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>6</v>
-      </c>
       <c r="F8" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:6">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="1">
-        <v>4</v>
-      </c>
-      <c r="D9" s="1">
-        <v>4</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="4" t="s">
+    <row r="10" customHeight="1" spans="3:7">
+      <c r="C10" s="1">
         <v>11</v>
       </c>
+      <c r="D10" s="1">
+        <v>2</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="10" customHeight="1" spans="1:6">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="1">
-        <v>5</v>
-      </c>
-      <c r="D10" s="1">
-        <v>5</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" s="4" t="s">
+    <row r="11" customHeight="1" spans="3:7">
+      <c r="C11" s="1">
         <v>12</v>
       </c>
+      <c r="D11" s="1">
+        <v>2</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="11" customHeight="1" spans="1:6">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="1">
-        <v>6</v>
-      </c>
-      <c r="D11" s="1">
-        <v>6</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" s="4" t="s">
+    <row r="12" customHeight="1" spans="3:7">
+      <c r="C12" s="1">
         <v>13</v>
+      </c>
+      <c r="D12" s="1">
+        <v>2</v>
+      </c>
+      <c r="E12" s="1">
+        <v>3</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:7">
+      <c r="C15" s="1">
+        <v>21</v>
+      </c>
+      <c r="D15" s="1">
+        <v>3</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:7">
+      <c r="C16" s="1">
+        <v>22</v>
+      </c>
+      <c r="D16" s="1">
+        <v>3</v>
+      </c>
+      <c r="E16" s="1">
+        <v>2</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:7">
+      <c r="C17" s="1">
+        <v>23</v>
+      </c>
+      <c r="D17" s="1">
+        <v>3</v>
+      </c>
+      <c r="E17" s="1">
+        <v>3</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:F3 E4:F5" errorStyle="warning">
-      <formula1>COUNTIF($C:$C,E3)&lt;2</formula1>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3:G5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,F3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Excel/ExclusiveDevourConfig.xlsx
+++ b/Excel/ExclusiveDevourConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="16">
   <si>
     <t>Id</t>
   </si>
@@ -65,25 +65,16 @@
     <t>4035,4010</t>
   </si>
   <si>
-    <t>150,300</t>
-  </si>
-  <si>
-    <t>450,900</t>
-  </si>
-  <si>
-    <t>1350,2700</t>
+    <t>150,3000</t>
+  </si>
+  <si>
+    <t>450,6000</t>
+  </si>
+  <si>
+    <t>1350,12000</t>
   </si>
   <si>
     <t>4036,4010</t>
-  </si>
-  <si>
-    <t>150,1000</t>
-  </si>
-  <si>
-    <t>450,3000</t>
-  </si>
-  <si>
-    <t>1350,9000</t>
   </si>
 </sst>
 </file>
@@ -1255,7 +1246,7 @@
         <v>15</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:7">
@@ -1272,7 +1263,7 @@
         <v>15</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:7">
@@ -1289,7 +1280,7 @@
         <v>15</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/ExclusiveDevourConfig.xlsx
+++ b/Excel/ExclusiveDevourConfig.xlsx
@@ -74,7 +74,7 @@
     <t>1350,12000</t>
   </si>
   <si>
-    <t>4036,4010</t>
+    <t>4039,4010</t>
   </si>
 </sst>
 </file>

--- a/Excel/ExclusiveDevourConfig.xlsx
+++ b/Excel/ExclusiveDevourConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="19">
   <si>
     <t>Id</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Cycle</t>
   </si>
   <si>
-    <t>Level</t>
+    <t>Layer</t>
   </si>
   <si>
     <t>ItemIdList</t>
@@ -44,6 +44,12 @@
     <t>ItemCountList</t>
   </si>
   <si>
+    <t>UpItemIdList</t>
+  </si>
+  <si>
+    <t>UpItemCountList</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -66,6 +72,9 @@
   </si>
   <si>
     <t>150,3000</t>
+  </si>
+  <si>
+    <t>40,400</t>
   </si>
   <si>
     <t>450,6000</t>
@@ -1070,16 +1079,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:G17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="6"/>
+  <dimension ref="C3:I17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="5" width="9" style="1"/>
     <col min="6" max="6" width="17.3727272727273" style="1" customWidth="1"/>
     <col min="7" max="7" width="13.5" style="1" customWidth="1"/>
-    <col min="8" max="16380" width="9" style="1"/>
+    <col min="8" max="8" width="17.3727272727273" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5" style="1" customWidth="1"/>
+    <col min="10" max="16380" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:7">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1095,8 +1106,14 @@
       <c r="G3" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="H3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:7">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1112,22 +1129,34 @@
       <c r="G4" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="H4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:7">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C5" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="3:7">
@@ -1141,10 +1170,10 @@
         <v>1</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:7">
@@ -1158,10 +1187,10 @@
         <v>2</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="3:7">
@@ -1175,13 +1204,13 @@
         <v>3</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="3:7">
+    <row r="10" customHeight="1" spans="3:9">
       <c r="C10" s="1">
         <v>11</v>
       </c>
@@ -1192,13 +1221,19 @@
         <v>1</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="3:7">
+    <row r="11" customHeight="1" spans="3:9">
       <c r="C11" s="1">
         <v>12</v>
       </c>
@@ -1209,13 +1244,19 @@
         <v>2</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="I11" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="12" customHeight="1" spans="3:7">
+    <row r="12" customHeight="1" spans="3:9">
       <c r="C12" s="1">
         <v>13</v>
       </c>
@@ -1226,13 +1267,19 @@
         <v>3</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="3:7">
+    <row r="15" customHeight="1" spans="3:9">
       <c r="C15" s="1">
         <v>21</v>
       </c>
@@ -1243,13 +1290,19 @@
         <v>1</v>
       </c>
       <c r="F15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G15" s="4" t="s">
-        <v>12</v>
-      </c>
     </row>
-    <row r="16" customHeight="1" spans="3:7">
+    <row r="16" customHeight="1" spans="3:9">
       <c r="C16" s="1">
         <v>22</v>
       </c>
@@ -1260,13 +1313,19 @@
         <v>2</v>
       </c>
       <c r="F16" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="4" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="17" customHeight="1" spans="3:7">
+    <row r="17" customHeight="1" spans="3:9">
       <c r="C17" s="1">
         <v>23</v>
       </c>
@@ -1277,15 +1336,21 @@
         <v>3</v>
       </c>
       <c r="F17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3:G5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="H3:I3 H4:I4 H5:I5 F3:G5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,F3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/ExclusiveDevourConfig.xlsx
+++ b/Excel/ExclusiveDevourConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="22">
   <si>
     <t>Id</t>
   </si>
@@ -84,6 +84,15 @@
   </si>
   <si>
     <t>4039,4010</t>
+  </si>
+  <si>
+    <t>150,5000</t>
+  </si>
+  <si>
+    <t>450,10000</t>
+  </si>
+  <si>
+    <t>1350,20000</t>
   </si>
 </sst>
 </file>
@@ -1293,7 +1302,7 @@
         <v>18</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>18</v>
@@ -1316,7 +1325,7 @@
         <v>18</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>18</v>
@@ -1339,7 +1348,7 @@
         <v>18</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>18</v>
@@ -1350,7 +1359,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="H3:I3 H4:I4 H5:I5 F3:G5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3:I5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,F3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/ExclusiveDevourConfig.xlsx
+++ b/Excel/ExclusiveDevourConfig.xlsx
@@ -74,7 +74,7 @@
     <t>150,3000</t>
   </si>
   <si>
-    <t>40,400</t>
+    <t>40,1000</t>
   </si>
   <si>
     <t>450,6000</t>

--- a/Excel/ExclusiveDevourConfig.xlsx
+++ b/Excel/ExclusiveDevourConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="22">
   <si>
     <t>Id</t>
   </si>
@@ -1088,7 +1088,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I17"/>
+  <dimension ref="C3:I21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="5" width="9" style="1"/>
@@ -1168,7 +1168,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="3:7">
+    <row r="6" customHeight="1" spans="3:9">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1185,7 +1185,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="3:7">
+    <row r="7" customHeight="1" spans="3:9">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1202,7 +1202,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1" spans="3:7">
+    <row r="8" ht="20" customHeight="1" spans="3:9">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1354,6 +1354,75 @@
         <v>18</v>
       </c>
       <c r="I17" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:9">
+      <c r="C19" s="1">
+        <v>31</v>
+      </c>
+      <c r="D19" s="1">
+        <v>4</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:9">
+      <c r="C20" s="1">
+        <v>32</v>
+      </c>
+      <c r="D20" s="1">
+        <v>4</v>
+      </c>
+      <c r="E20" s="1">
+        <v>2</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:9">
+      <c r="C21" s="1">
+        <v>33</v>
+      </c>
+      <c r="D21" s="1">
+        <v>4</v>
+      </c>
+      <c r="E21" s="1">
+        <v>3</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="4" t="s">
         <v>15</v>
       </c>
     </row>

--- a/Excel/ExclusiveDevourConfig.xlsx
+++ b/Excel/ExclusiveDevourConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="26">
   <si>
     <t>Id</t>
   </si>
@@ -93,6 +93,18 @@
   </si>
   <si>
     <t>1350,20000</t>
+  </si>
+  <si>
+    <t>4037,4010</t>
+  </si>
+  <si>
+    <t>150,10000</t>
+  </si>
+  <si>
+    <t>450,20000</t>
+  </si>
+  <si>
+    <t>1350,40000</t>
   </si>
 </sst>
 </file>
@@ -1368,10 +1380,10 @@
         <v>1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>18</v>
@@ -1391,10 +1403,10 @@
         <v>2</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>18</v>
@@ -1414,10 +1426,10 @@
         <v>3</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>18</v>
